--- a/results/reports/year_2020_report.xlsx
+++ b/results/reports/year_2020_report.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,30 +505,40 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>top_30_return_compounded</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>top_30_excess</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>decile_return_compounded</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>decile_excess</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>OMXS30_return</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>OMXC25_return</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>OMXH25_return</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>OSEBX_return</t>
         </is>
@@ -572,15 +582,21 @@
         <v>18.56</v>
       </c>
       <c r="M2" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="N2" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="O2" t="n">
         <v>16.94</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>16.12</v>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -739,7 +755,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.612601165382905</v>
+        <v>0.6126011653829049</v>
       </c>
       <c r="E7" t="n">
         <v>28.291</v>
@@ -759,7 +775,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6100219960896807</v>
+        <v>0.6100219960896806</v>
       </c>
       <c r="E8" t="n">
         <v>-6.1078</v>
@@ -859,7 +875,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.5954425626953203</v>
+        <v>0.5954425626953204</v>
       </c>
       <c r="E13" t="n">
         <v>9.502599999999999</v>
@@ -1245,7 +1261,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.606941882740512</v>
+        <v>0.6069418827405119</v>
       </c>
       <c r="E10" t="n">
         <v>15.7141</v>
@@ -1285,7 +1301,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.598230386825489</v>
+        <v>0.5982303868254891</v>
       </c>
       <c r="E12" t="n">
         <v>-1.506</v>
@@ -1305,7 +1321,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.5966664563854563</v>
+        <v>0.5966664563854561</v>
       </c>
       <c r="E13" t="n">
         <v>15.6033</v>
@@ -1325,7 +1341,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.5957026090858333</v>
+        <v>0.5957026090858334</v>
       </c>
       <c r="E14" t="n">
         <v>2.9064</v>
@@ -1385,7 +1401,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5944468363820877</v>
+        <v>0.5944468363820878</v>
       </c>
       <c r="E17" t="n">
         <v>7.8798</v>
@@ -1571,7 +1587,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6164071667253931</v>
+        <v>0.6164071667253932</v>
       </c>
       <c r="E4" t="n">
         <v>-15.0699</v>
@@ -1591,7 +1607,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6137039986930521</v>
+        <v>0.6137039986930523</v>
       </c>
       <c r="E5" t="n">
         <v>8.349500000000001</v>
@@ -1611,7 +1627,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6131818986506632</v>
+        <v>0.613181898650663</v>
       </c>
       <c r="E6" t="n">
         <v>-10.1563</v>
@@ -1631,7 +1647,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6067524937143236</v>
+        <v>0.6067524937143237</v>
       </c>
       <c r="E7" t="n">
         <v>-4.8346</v>
@@ -1791,7 +1807,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.5895479367350592</v>
+        <v>0.5895479367350593</v>
       </c>
       <c r="E15" t="n">
         <v>11.1357</v>
@@ -1831,7 +1847,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.589279041257823</v>
+        <v>0.5892790412578232</v>
       </c>
       <c r="E17" t="n">
         <v>-9.940899999999999</v>
@@ -1911,7 +1927,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.5868804824405465</v>
+        <v>0.5868804824405466</v>
       </c>
       <c r="E21" t="n">
         <v>16.1325</v>
@@ -1997,7 +2013,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6736048823263802</v>
+        <v>0.6736048823263801</v>
       </c>
       <c r="E3" t="n">
         <v>4.7312</v>
@@ -2017,7 +2033,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6462394600606326</v>
+        <v>0.6462394600606328</v>
       </c>
       <c r="E4" t="n">
         <v>-0.7667</v>
@@ -2037,7 +2053,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6424168336301322</v>
+        <v>0.6424168336301321</v>
       </c>
       <c r="E5" t="n">
         <v>5.7808</v>
@@ -2057,7 +2073,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6404588281278163</v>
+        <v>0.6404588281278162</v>
       </c>
       <c r="E6" t="n">
         <v>13.6345</v>
@@ -2097,7 +2113,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6222366212513821</v>
+        <v>0.6222366212513822</v>
       </c>
       <c r="E8" t="n">
         <v>5.2296</v>
@@ -2117,7 +2133,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6183504095006475</v>
+        <v>0.6183504095006476</v>
       </c>
       <c r="E9" t="n">
         <v>13.7925</v>
@@ -2137,7 +2153,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6160107344228841</v>
+        <v>0.616010734422884</v>
       </c>
       <c r="E10" t="n">
         <v>12.4348</v>
@@ -2157,7 +2173,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6145987943589183</v>
+        <v>0.6145987943589182</v>
       </c>
       <c r="E11" t="n">
         <v>8.8009</v>
@@ -2237,7 +2253,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6047523568315705</v>
+        <v>0.6047523568315704</v>
       </c>
       <c r="E15" t="n">
         <v>-13.5054</v>
@@ -2583,7 +2599,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.5990839280782418</v>
+        <v>0.5990839280782417</v>
       </c>
       <c r="E10" t="n">
         <v>7.957</v>
@@ -2623,7 +2639,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.5913920820502739</v>
+        <v>0.591392082050274</v>
       </c>
       <c r="E12" t="n">
         <v>4.3947</v>
@@ -2643,7 +2659,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.59074226589267</v>
+        <v>0.5907422658926699</v>
       </c>
       <c r="E13" t="n">
         <v>5.1579</v>
@@ -2723,7 +2739,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5867019887739784</v>
+        <v>0.5867019887739783</v>
       </c>
       <c r="E17" t="n">
         <v>16.7418</v>
@@ -2743,7 +2759,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.5852654018245091</v>
+        <v>0.5852654018245093</v>
       </c>
       <c r="E18" t="n">
         <v>2.1277</v>
@@ -2783,7 +2799,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.5829587939373199</v>
+        <v>0.58295879393732</v>
       </c>
       <c r="E20" t="n">
         <v>5.9784</v>
@@ -2869,7 +2885,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6382427958641637</v>
+        <v>0.6382427958641638</v>
       </c>
       <c r="E2" t="n">
         <v>13.3481</v>
@@ -2949,7 +2965,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6019391050094134</v>
+        <v>0.6019391050094135</v>
       </c>
       <c r="E6" t="n">
         <v>1.8447</v>
@@ -2969,7 +2985,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.5996044642229679</v>
+        <v>0.599604464222968</v>
       </c>
       <c r="E7" t="n">
         <v>-4.0312</v>
@@ -3029,7 +3045,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.5928863458959068</v>
+        <v>0.5928863458959069</v>
       </c>
       <c r="E10" t="n">
         <v>8.7674</v>
@@ -3129,7 +3145,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.5839061048152753</v>
+        <v>0.5839061048152754</v>
       </c>
       <c r="E15" t="n">
         <v>-6.7661</v>
@@ -3149,7 +3165,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.5831922254556615</v>
+        <v>0.5831922254556614</v>
       </c>
       <c r="E16" t="n">
         <v>0.2941</v>
@@ -3169,7 +3185,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5830697447288586</v>
+        <v>0.5830697447288588</v>
       </c>
       <c r="E17" t="n">
         <v>3.5971</v>
@@ -3189,7 +3205,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.5820989367011425</v>
+        <v>0.5820989367011427</v>
       </c>
       <c r="E18" t="n">
         <v>-0.2917</v>
@@ -3269,7 +3285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3290,25 +3306,30 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>top_30_return</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>decile_return</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>OMXS30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>OMXC25</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>OMXH25</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>OSEBX</t>
         </is>
@@ -3325,12 +3346,15 @@
         <v>-6.16</v>
       </c>
       <c r="D2" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="E2" t="n">
         <v>-5.83</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -3343,12 +3367,15 @@
         <v>-15.27</v>
       </c>
       <c r="D3" t="n">
+        <v>-17.15</v>
+      </c>
+      <c r="E3" t="n">
         <v>-15.96</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3361,12 +3388,15 @@
         <v>9.970000000000001</v>
       </c>
       <c r="D4" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="E4" t="n">
         <v>9.449999999999999</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -3379,12 +3409,15 @@
         <v>3.12</v>
       </c>
       <c r="D5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E5" t="n">
         <v>5.58</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -3397,12 +3430,15 @@
         <v>2.02</v>
       </c>
       <c r="D6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="E6" t="n">
         <v>1.79</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -3415,12 +3451,15 @@
         <v>2.73</v>
       </c>
       <c r="D7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E7" t="n">
         <v>3.97</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -3433,12 +3472,15 @@
         <v>4.93</v>
       </c>
       <c r="D8" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="E8" t="n">
         <v>4.6</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -3451,12 +3493,15 @@
         <v>4.13</v>
       </c>
       <c r="D9" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="E9" t="n">
         <v>4.12</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -3469,12 +3514,15 @@
         <v>0.04</v>
       </c>
       <c r="D10" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="E10" t="n">
         <v>-3.57</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -3487,12 +3535,15 @@
         <v>8.279999999999999</v>
       </c>
       <c r="D11" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="E11" t="n">
         <v>8.01</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -3505,12 +3556,15 @@
         <v>6.38</v>
       </c>
       <c r="D12" t="n">
+        <v>7.23</v>
+      </c>
+      <c r="E12" t="n">
         <v>5.71</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -3523,12 +3577,15 @@
         <v>0.33</v>
       </c>
       <c r="D13" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.78</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3913,7 +3970,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6826018207744805</v>
+        <v>0.6826018207744804</v>
       </c>
       <c r="E7" t="n">
         <v>2.4377</v>
@@ -4013,7 +4070,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6697033989195101</v>
+        <v>0.6697033989195103</v>
       </c>
       <c r="E12" t="n">
         <v>-11.3877</v>
@@ -4033,7 +4090,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6573701339562505</v>
+        <v>0.6573701339562507</v>
       </c>
       <c r="E13" t="n">
         <v>-4.8442</v>
@@ -4053,7 +4110,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6572238529853149</v>
+        <v>0.6572238529853148</v>
       </c>
       <c r="E14" t="n">
         <v>0.5649999999999999</v>
@@ -4113,7 +4170,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6455564595686163</v>
+        <v>0.6455564595686164</v>
       </c>
       <c r="E17" t="n">
         <v>-15.878</v>
@@ -4133,7 +4190,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6448888989668844</v>
+        <v>0.6448888989668845</v>
       </c>
       <c r="E18" t="n">
         <v>-7.7519</v>
@@ -4259,7 +4316,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7530026384727031</v>
+        <v>0.753002638472703</v>
       </c>
       <c r="E2" t="n">
         <v>-32.5198</v>
@@ -4379,7 +4436,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.7026958381856646</v>
+        <v>0.7026958381856645</v>
       </c>
       <c r="E8" t="n">
         <v>-18.381</v>
@@ -4499,7 +4556,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.687076759901056</v>
+        <v>0.6870767599010559</v>
       </c>
       <c r="E14" t="n">
         <v>-6.802</v>
@@ -4619,7 +4676,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6484091132469746</v>
+        <v>0.6484091132469745</v>
       </c>
       <c r="E20" t="n">
         <v>-5.8824</v>
@@ -4639,7 +4696,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6480689378742673</v>
+        <v>0.6480689378742671</v>
       </c>
       <c r="E21" t="n">
         <v>-20.6459</v>
@@ -4705,7 +4762,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6402963866833535</v>
+        <v>0.6402963866833536</v>
       </c>
       <c r="E2" t="n">
         <v>-3.0983</v>
@@ -4785,7 +4842,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.5827300910929427</v>
+        <v>0.5827300910929426</v>
       </c>
       <c r="E6" t="n">
         <v>-8.917199999999999</v>
@@ -4805,7 +4862,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.5767028683915723</v>
+        <v>0.5767028683915721</v>
       </c>
       <c r="E7" t="n">
         <v>11.3358</v>
@@ -4905,7 +4962,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.5571134104692552</v>
+        <v>0.5571134104692551</v>
       </c>
       <c r="E12" t="n">
         <v>9.777799999999999</v>
@@ -5005,7 +5062,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.546973792909117</v>
+        <v>0.5469737929091169</v>
       </c>
       <c r="E17" t="n">
         <v>32.6606</v>
@@ -5411,7 +5468,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.5776568691217169</v>
+        <v>0.577656869121717</v>
       </c>
       <c r="E15" t="n">
         <v>0.1894</v>
@@ -5451,7 +5508,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5742928459110621</v>
+        <v>0.5742928459110622</v>
       </c>
       <c r="E17" t="n">
         <v>-5.5891</v>
@@ -5491,7 +5548,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.5728289468760607</v>
+        <v>0.5728289468760606</v>
       </c>
       <c r="E19" t="n">
         <v>2.9693</v>
@@ -5597,7 +5654,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.666969393397697</v>
+        <v>0.6669693933976969</v>
       </c>
       <c r="E2" t="n">
         <v>0.9384</v>
@@ -5617,7 +5674,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6358286834408188</v>
+        <v>0.6358286834408187</v>
       </c>
       <c r="E3" t="n">
         <v>-3.3557</v>
@@ -5637,7 +5694,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6067831854042627</v>
+        <v>0.6067831854042628</v>
       </c>
       <c r="E4" t="n">
         <v>13.3333</v>
@@ -5677,7 +5734,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.5922841223474433</v>
+        <v>0.5922841223474432</v>
       </c>
       <c r="E6" t="n">
         <v>0.9827</v>
@@ -5757,7 +5814,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.5787576518032839</v>
+        <v>0.578757651803284</v>
       </c>
       <c r="E10" t="n">
         <v>-2.9534</v>
@@ -5817,7 +5874,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.5767195806899652</v>
+        <v>0.5767195806899651</v>
       </c>
       <c r="E13" t="n">
         <v>-4.6707</v>
@@ -5917,7 +5974,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.5746800326129231</v>
+        <v>0.5746800326129232</v>
       </c>
       <c r="E18" t="n">
         <v>6.1331</v>
@@ -5957,7 +6014,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.5741682256922862</v>
+        <v>0.5741682256922863</v>
       </c>
       <c r="E20" t="n">
         <v>0.5593</v>
@@ -6163,7 +6220,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6147727416394467</v>
+        <v>0.6147727416394468</v>
       </c>
       <c r="E8" t="n">
         <v>9.9048</v>
@@ -6323,7 +6380,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.5988567435250561</v>
+        <v>0.5988567435250562</v>
       </c>
       <c r="E16" t="n">
         <v>3.5313</v>
@@ -6343,7 +6400,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5951598554732291</v>
+        <v>0.5951598554732292</v>
       </c>
       <c r="E17" t="n">
         <v>9.9901</v>
@@ -6363,7 +6420,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.5943667585538186</v>
+        <v>0.5943667585538187</v>
       </c>
       <c r="E18" t="n">
         <v>5.5125</v>
@@ -6403,7 +6460,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.5924259496958492</v>
+        <v>0.5924259496958493</v>
       </c>
       <c r="E20" t="n">
         <v>-1.8915</v>

--- a/results/reports/year_2020_report.xlsx
+++ b/results/reports/year_2020_report.xlsx
@@ -755,7 +755,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6126011653829049</v>
+        <v>0.612601165382905</v>
       </c>
       <c r="E7" t="n">
         <v>28.291</v>
@@ -775,7 +775,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6100219960896806</v>
+        <v>0.6100219960896807</v>
       </c>
       <c r="E8" t="n">
         <v>-6.1078</v>
@@ -835,7 +835,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.5986805939917456</v>
+        <v>0.5986805939917454</v>
       </c>
       <c r="E11" t="n">
         <v>2.19</v>
@@ -955,7 +955,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5918139786712253</v>
+        <v>0.5918139786712252</v>
       </c>
       <c r="E17" t="n">
         <v>3.3683</v>
@@ -995,7 +995,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.5912339075487211</v>
+        <v>0.5912339075487212</v>
       </c>
       <c r="E19" t="n">
         <v>-1.3614</v>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.5912207377005942</v>
+        <v>0.5912207377005941</v>
       </c>
       <c r="E20" t="n">
         <v>13.5587</v>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.635510415597153</v>
+        <v>0.6355104155971529</v>
       </c>
       <c r="E3" t="n">
         <v>-2.2901</v>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.619940256713114</v>
+        <v>0.6199402567131139</v>
       </c>
       <c r="E6" t="n">
         <v>7.2204</v>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6089563462446977</v>
+        <v>0.6089563462446979</v>
       </c>
       <c r="E9" t="n">
         <v>1.8584</v>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6069418827405119</v>
+        <v>0.606941882740512</v>
       </c>
       <c r="E10" t="n">
         <v>15.7141</v>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6068111677447418</v>
+        <v>0.6068111677447416</v>
       </c>
       <c r="E11" t="n">
         <v>15.0426</v>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.5982303868254891</v>
+        <v>0.598230386825489</v>
       </c>
       <c r="E12" t="n">
         <v>-1.506</v>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.5966664563854561</v>
+        <v>0.5966664563854562</v>
       </c>
       <c r="E13" t="n">
         <v>15.6033</v>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.5947843825468315</v>
+        <v>0.5947843825468316</v>
       </c>
       <c r="E16" t="n">
         <v>1.2427</v>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5944468363820878</v>
+        <v>0.5944468363820877</v>
       </c>
       <c r="E17" t="n">
         <v>7.8798</v>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.5919477411650991</v>
+        <v>0.591947741165099</v>
       </c>
       <c r="E20" t="n">
         <v>-6.6824</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6415691258513861</v>
+        <v>0.641569125851386</v>
       </c>
       <c r="E2" t="n">
         <v>0.0333</v>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6164071667253932</v>
+        <v>0.6164071667253931</v>
       </c>
       <c r="E4" t="n">
         <v>-15.0699</v>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6137039986930523</v>
+        <v>0.6137039986930521</v>
       </c>
       <c r="E5" t="n">
         <v>8.349500000000001</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.613181898650663</v>
+        <v>0.6131818986506631</v>
       </c>
       <c r="E6" t="n">
         <v>-10.1563</v>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6021513893971936</v>
+        <v>0.6021513893971935</v>
       </c>
       <c r="E9" t="n">
         <v>-4.4125</v>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.5893941089799586</v>
+        <v>0.5893941089799585</v>
       </c>
       <c r="E16" t="n">
         <v>-3.7037</v>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5892790412578232</v>
+        <v>0.589279041257823</v>
       </c>
       <c r="E17" t="n">
         <v>-9.940899999999999</v>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.5882985505334107</v>
+        <v>0.5882985505334106</v>
       </c>
       <c r="E19" t="n">
         <v>0.8439</v>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6462394600606328</v>
+        <v>0.6462394600606326</v>
       </c>
       <c r="E4" t="n">
         <v>-0.7667</v>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6404588281278162</v>
+        <v>0.6404588281278163</v>
       </c>
       <c r="E6" t="n">
         <v>13.6345</v>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.616010734422884</v>
+        <v>0.6160107344228841</v>
       </c>
       <c r="E10" t="n">
         <v>12.4348</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6048714287591747</v>
+        <v>0.6048714287591745</v>
       </c>
       <c r="E14" t="n">
         <v>-0.9699</v>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.593100549528469</v>
+        <v>0.5931005495284691</v>
       </c>
       <c r="E17" t="n">
         <v>22.5942</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6465885007528608</v>
+        <v>0.646588500752861</v>
       </c>
       <c r="E4" t="n">
         <v>0.7921</v>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6028271388021449</v>
+        <v>0.602827138802145</v>
       </c>
       <c r="E7" t="n">
         <v>5.3802</v>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.5990839280782417</v>
+        <v>0.599083928078242</v>
       </c>
       <c r="E10" t="n">
         <v>7.957</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.5890904376722446</v>
+        <v>0.5890904376722444</v>
       </c>
       <c r="E14" t="n">
         <v>-2.0575</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6382427958641638</v>
+        <v>0.6382427958641637</v>
       </c>
       <c r="E2" t="n">
         <v>13.3481</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6126536147031739</v>
+        <v>0.6126536147031738</v>
       </c>
       <c r="E3" t="n">
         <v>-3.7573</v>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6019391050094135</v>
+        <v>0.6019391050094134</v>
       </c>
       <c r="E6" t="n">
         <v>1.8447</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.599604464222968</v>
+        <v>0.5996044642229679</v>
       </c>
       <c r="E7" t="n">
         <v>-4.0312</v>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.5928863458959069</v>
+        <v>0.5928863458959068</v>
       </c>
       <c r="E10" t="n">
         <v>8.7674</v>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.5851456710959644</v>
+        <v>0.5851456710959645</v>
       </c>
       <c r="E14" t="n">
         <v>0.3655</v>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.5831922254556614</v>
+        <v>0.5831922254556615</v>
       </c>
       <c r="E16" t="n">
         <v>0.2941</v>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5830697447288588</v>
+        <v>0.5830697447288586</v>
       </c>
       <c r="E17" t="n">
         <v>3.5971</v>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.5820989367011427</v>
+        <v>0.5820989367011425</v>
       </c>
       <c r="E18" t="n">
         <v>-0.2917</v>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.712326316900042</v>
+        <v>0.7123263169000421</v>
       </c>
       <c r="E3" t="n">
         <v>-1.1933</v>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6972048860488279</v>
+        <v>0.6972048860488278</v>
       </c>
       <c r="E5" t="n">
         <v>-2.4543</v>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6826018207744804</v>
+        <v>0.6826018207744805</v>
       </c>
       <c r="E7" t="n">
         <v>2.4377</v>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6697033989195103</v>
+        <v>0.6697033989195101</v>
       </c>
       <c r="E12" t="n">
         <v>-11.3877</v>
@@ -4110,7 +4110,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6572238529853148</v>
+        <v>0.6572238529853149</v>
       </c>
       <c r="E14" t="n">
         <v>0.5649999999999999</v>
@@ -4150,7 +4150,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6464980058496126</v>
+        <v>0.6464980058496127</v>
       </c>
       <c r="E16" t="n">
         <v>-5.1789</v>
@@ -4316,7 +4316,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.753002638472703</v>
+        <v>0.7530026384727031</v>
       </c>
       <c r="E2" t="n">
         <v>-32.5198</v>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.68797626483235</v>
+        <v>0.6879762648323501</v>
       </c>
       <c r="E13" t="n">
         <v>2.9982</v>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6870767599010559</v>
+        <v>0.687076759901056</v>
       </c>
       <c r="E14" t="n">
         <v>-6.802</v>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6821264269359874</v>
+        <v>0.6821264269359876</v>
       </c>
       <c r="E15" t="n">
         <v>-23.7368</v>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6632825552601704</v>
+        <v>0.6632825552601705</v>
       </c>
       <c r="E16" t="n">
         <v>-22.4767</v>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6484091132469745</v>
+        <v>0.6484091132469746</v>
       </c>
       <c r="E20" t="n">
         <v>-5.8824</v>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.5912148337617085</v>
+        <v>0.5912148337617086</v>
       </c>
       <c r="E5" t="n">
         <v>7.3851</v>
@@ -4962,7 +4962,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.5571134104692551</v>
+        <v>0.5571134104692552</v>
       </c>
       <c r="E12" t="n">
         <v>9.777799999999999</v>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5469737929091169</v>
+        <v>0.546973792909117</v>
       </c>
       <c r="E17" t="n">
         <v>32.6606</v>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.5450263117000496</v>
+        <v>0.5450263117000494</v>
       </c>
       <c r="E21" t="n">
         <v>21.7101</v>
@@ -5468,7 +5468,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.577656869121717</v>
+        <v>0.5776568691217169</v>
       </c>
       <c r="E15" t="n">
         <v>0.1894</v>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.5736766975495763</v>
+        <v>0.5736766975495761</v>
       </c>
       <c r="E18" t="n">
         <v>-2.7778</v>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.5728289468760606</v>
+        <v>0.5728289468760607</v>
       </c>
       <c r="E19" t="n">
         <v>2.9693</v>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6358286834408187</v>
+        <v>0.6358286834408188</v>
       </c>
       <c r="E3" t="n">
         <v>-3.3557</v>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6067831854042628</v>
+        <v>0.6067831854042627</v>
       </c>
       <c r="E4" t="n">
         <v>13.3333</v>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.5922841223474432</v>
+        <v>0.5922841223474433</v>
       </c>
       <c r="E6" t="n">
         <v>0.9827</v>
@@ -5854,7 +5854,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.5779570007552984</v>
+        <v>0.5779570007552983</v>
       </c>
       <c r="E12" t="n">
         <v>1.2426</v>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.5767195806899651</v>
+        <v>0.5767195806899652</v>
       </c>
       <c r="E13" t="n">
         <v>-4.6707</v>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.5751142091943194</v>
+        <v>0.5751142091943193</v>
       </c>
       <c r="E16" t="n">
         <v>-3.6996</v>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.5746800326129232</v>
+        <v>0.5746800326129231</v>
       </c>
       <c r="E18" t="n">
         <v>6.1331</v>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.5741682256922863</v>
+        <v>0.5741682256922862</v>
       </c>
       <c r="E20" t="n">
         <v>0.5593</v>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6644021289054632</v>
+        <v>0.6644021289054634</v>
       </c>
       <c r="E2" t="n">
         <v>3.6592</v>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6511347991733318</v>
+        <v>0.6511347991733319</v>
       </c>
       <c r="E3" t="n">
         <v>4.9299</v>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6131099369451863</v>
+        <v>0.6131099369451861</v>
       </c>
       <c r="E11" t="n">
         <v>-2.7778</v>
@@ -6400,7 +6400,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5951598554732292</v>
+        <v>0.5951598554732291</v>
       </c>
       <c r="E17" t="n">
         <v>9.9901</v>
@@ -6460,7 +6460,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.5924259496958493</v>
+        <v>0.5924259496958494</v>
       </c>
       <c r="E20" t="n">
         <v>-1.8915</v>

--- a/results/reports/year_2020_report.xlsx
+++ b/results/reports/year_2020_report.xlsx
@@ -815,7 +815,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.5992363174497097</v>
+        <v>0.5992363174497096</v>
       </c>
       <c r="E10" t="n">
         <v>3.5108</v>
@@ -835,7 +835,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.5986805939917454</v>
+        <v>0.5986805939917456</v>
       </c>
       <c r="E11" t="n">
         <v>2.19</v>
@@ -895,7 +895,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.5944420282394688</v>
+        <v>0.5944420282394689</v>
       </c>
       <c r="E14" t="n">
         <v>8.261200000000001</v>
@@ -995,7 +995,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.5912339075487212</v>
+        <v>0.5912339075487211</v>
       </c>
       <c r="E19" t="n">
         <v>-1.3614</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6429876464684111</v>
+        <v>0.6429876464684109</v>
       </c>
       <c r="E2" t="n">
         <v>14.441</v>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6355104155971529</v>
+        <v>0.6355104155971528</v>
       </c>
       <c r="E3" t="n">
         <v>-2.2901</v>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6089563462446979</v>
+        <v>0.6089563462446977</v>
       </c>
       <c r="E9" t="n">
         <v>1.8584</v>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.598230386825489</v>
+        <v>0.5982303868254891</v>
       </c>
       <c r="E12" t="n">
         <v>-1.506</v>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.5947843825468316</v>
+        <v>0.5947843825468315</v>
       </c>
       <c r="E16" t="n">
         <v>1.2427</v>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5944468363820877</v>
+        <v>0.5944468363820878</v>
       </c>
       <c r="E17" t="n">
         <v>7.8798</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.5936493853011949</v>
+        <v>0.593649385301195</v>
       </c>
       <c r="E18" t="n">
         <v>0.4423</v>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.591947741165099</v>
+        <v>0.5919477411650991</v>
       </c>
       <c r="E20" t="n">
         <v>-6.6824</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.641569125851386</v>
+        <v>0.6415691258513861</v>
       </c>
       <c r="E2" t="n">
         <v>0.0333</v>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6164071667253931</v>
+        <v>0.6164071667253932</v>
       </c>
       <c r="E4" t="n">
         <v>-15.0699</v>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6137039986930521</v>
+        <v>0.6137039986930523</v>
       </c>
       <c r="E5" t="n">
         <v>8.349500000000001</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6131818986506631</v>
+        <v>0.613181898650663</v>
       </c>
       <c r="E6" t="n">
         <v>-10.1563</v>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6021513893971935</v>
+        <v>0.6021513893971936</v>
       </c>
       <c r="E9" t="n">
         <v>-4.4125</v>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.5962466714368625</v>
+        <v>0.5962466714368626</v>
       </c>
       <c r="E11" t="n">
         <v>4.7341</v>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.589279041257823</v>
+        <v>0.5892790412578232</v>
       </c>
       <c r="E17" t="n">
         <v>-9.940899999999999</v>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.5882985505334106</v>
+        <v>0.5882985505334107</v>
       </c>
       <c r="E19" t="n">
         <v>0.8439</v>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6462394600606326</v>
+        <v>0.6462394600606328</v>
       </c>
       <c r="E4" t="n">
         <v>-0.7667</v>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6404588281278163</v>
+        <v>0.6404588281278162</v>
       </c>
       <c r="E6" t="n">
         <v>13.6345</v>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6222366212513822</v>
+        <v>0.6222366212513821</v>
       </c>
       <c r="E8" t="n">
         <v>5.2296</v>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6183504095006476</v>
+        <v>0.6183504095006475</v>
       </c>
       <c r="E9" t="n">
         <v>13.7925</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.5936289249114505</v>
+        <v>0.5936289249114506</v>
       </c>
       <c r="E16" t="n">
         <v>4.6807</v>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.5903937569289363</v>
+        <v>0.5903937569289361</v>
       </c>
       <c r="E20" t="n">
         <v>4.5977</v>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.5899191274517095</v>
+        <v>0.5899191274517094</v>
       </c>
       <c r="E21" t="n">
         <v>10.151</v>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.652707213477145</v>
+        <v>0.6527072134771451</v>
       </c>
       <c r="E3" t="n">
         <v>2.0847</v>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.646588500752861</v>
+        <v>0.6465885007528608</v>
       </c>
       <c r="E4" t="n">
         <v>0.7921</v>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.602827138802145</v>
+        <v>0.6028271388021449</v>
       </c>
       <c r="E7" t="n">
         <v>5.3802</v>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6009097494829644</v>
+        <v>0.6009097494829645</v>
       </c>
       <c r="E8" t="n">
         <v>15.8157</v>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.599083928078242</v>
+        <v>0.5990839280782418</v>
       </c>
       <c r="E10" t="n">
         <v>7.957</v>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.5907422658926699</v>
+        <v>0.5907422658926701</v>
       </c>
       <c r="E13" t="n">
         <v>5.1579</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.5890904376722444</v>
+        <v>0.5890904376722446</v>
       </c>
       <c r="E14" t="n">
         <v>-2.0575</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5867019887739783</v>
+        <v>0.5867019887739784</v>
       </c>
       <c r="E17" t="n">
         <v>16.7418</v>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.58295879393732</v>
+        <v>0.5829587939373199</v>
       </c>
       <c r="E20" t="n">
         <v>5.9784</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6382427958641637</v>
+        <v>0.6382427958641638</v>
       </c>
       <c r="E2" t="n">
         <v>13.3481</v>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.5996044642229679</v>
+        <v>0.599604464222968</v>
       </c>
       <c r="E7" t="n">
         <v>-4.0312</v>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.5974953382398224</v>
+        <v>0.5974953382398225</v>
       </c>
       <c r="E9" t="n">
         <v>15.296</v>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.5831922254556615</v>
+        <v>0.5831922254556614</v>
       </c>
       <c r="E16" t="n">
         <v>0.2941</v>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5830697447288586</v>
+        <v>0.5830697447288588</v>
       </c>
       <c r="E17" t="n">
         <v>3.5971</v>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.5817359996995189</v>
+        <v>0.5817359996995191</v>
       </c>
       <c r="E19" t="n">
         <v>7</v>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.5800028071029772</v>
+        <v>0.5800028071029771</v>
       </c>
       <c r="E20" t="n">
         <v>-2.8429</v>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.5785307450095838</v>
+        <v>0.5785307450095839</v>
       </c>
       <c r="E21" t="n">
         <v>2.43</v>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7123263169000421</v>
+        <v>0.712326316900042</v>
       </c>
       <c r="E3" t="n">
         <v>-1.1933</v>
@@ -4110,7 +4110,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6572238529853149</v>
+        <v>0.6572238529853148</v>
       </c>
       <c r="E14" t="n">
         <v>0.5649999999999999</v>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.656730363235301</v>
+        <v>0.6567303632353009</v>
       </c>
       <c r="E15" t="n">
         <v>8.2456</v>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6455564595686164</v>
+        <v>0.6455564595686163</v>
       </c>
       <c r="E17" t="n">
         <v>-15.878</v>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6448888989668845</v>
+        <v>0.6448888989668844</v>
       </c>
       <c r="E18" t="n">
         <v>-7.7519</v>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.738629401477273</v>
+        <v>0.7386294014772729</v>
       </c>
       <c r="E4" t="n">
         <v>-3.717</v>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.7345452931898128</v>
+        <v>0.7345452931898125</v>
       </c>
       <c r="E5" t="n">
         <v>-4.0382</v>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.7142818541820354</v>
+        <v>0.7142818541820355</v>
       </c>
       <c r="E6" t="n">
         <v>2.0539</v>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6879762648323501</v>
+        <v>0.68797626483235</v>
       </c>
       <c r="E13" t="n">
         <v>2.9982</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6594008978973597</v>
+        <v>0.6594008978973595</v>
       </c>
       <c r="E17" t="n">
         <v>-4.8746</v>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.655131366705802</v>
+        <v>0.6551313667058021</v>
       </c>
       <c r="E19" t="n">
         <v>-33.4358</v>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6484091132469746</v>
+        <v>0.6484091132469745</v>
       </c>
       <c r="E20" t="n">
         <v>-5.8824</v>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6480689378742671</v>
+        <v>0.6480689378742673</v>
       </c>
       <c r="E21" t="n">
         <v>-20.6459</v>
@@ -4762,7 +4762,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6402963866833536</v>
+        <v>0.6402963866833535</v>
       </c>
       <c r="E2" t="n">
         <v>-3.0983</v>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.5912148337617086</v>
+        <v>0.5912148337617085</v>
       </c>
       <c r="E5" t="n">
         <v>7.3851</v>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.5827300910929426</v>
+        <v>0.5827300910929427</v>
       </c>
       <c r="E6" t="n">
         <v>-8.917199999999999</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.5767028683915721</v>
+        <v>0.5767028683915723</v>
       </c>
       <c r="E7" t="n">
         <v>11.3358</v>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.5672275535874169</v>
+        <v>0.5672275535874168</v>
       </c>
       <c r="E9" t="n">
         <v>5.6066</v>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.5517248545145299</v>
+        <v>0.5517248545145298</v>
       </c>
       <c r="E13" t="n">
         <v>31.6073</v>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6212182931089458</v>
+        <v>0.6212182931089457</v>
       </c>
       <c r="E3" t="n">
         <v>4.2026</v>
@@ -5268,7 +5268,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6186422271078634</v>
+        <v>0.6186422271078633</v>
       </c>
       <c r="E5" t="n">
         <v>10.0842</v>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.5736766975495761</v>
+        <v>0.5736766975495763</v>
       </c>
       <c r="E18" t="n">
         <v>-2.7778</v>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.5728289468760607</v>
+        <v>0.5728289468760606</v>
       </c>
       <c r="E19" t="n">
         <v>2.9693</v>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6669693933976969</v>
+        <v>0.666969393397697</v>
       </c>
       <c r="E2" t="n">
         <v>0.9384</v>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6358286834408188</v>
+        <v>0.6358286834408187</v>
       </c>
       <c r="E3" t="n">
         <v>-3.3557</v>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6067831854042627</v>
+        <v>0.6067831854042628</v>
       </c>
       <c r="E4" t="n">
         <v>13.3333</v>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.5942793403977271</v>
+        <v>0.594279340397727</v>
       </c>
       <c r="E5" t="n">
         <v>2.2409</v>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.5922841223474433</v>
+        <v>0.5922841223474434</v>
       </c>
       <c r="E6" t="n">
         <v>0.9827</v>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.5903226561585349</v>
+        <v>0.5903226561585347</v>
       </c>
       <c r="E7" t="n">
         <v>-0.0297</v>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.5818075313825886</v>
+        <v>0.5818075313825884</v>
       </c>
       <c r="E9" t="n">
         <v>9.649100000000001</v>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.578757651803284</v>
+        <v>0.5787576518032839</v>
       </c>
       <c r="E10" t="n">
         <v>-2.9534</v>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.578603810850537</v>
+        <v>0.5786038108505369</v>
       </c>
       <c r="E11" t="n">
         <v>-1.4765</v>
@@ -5854,7 +5854,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.5779570007552983</v>
+        <v>0.5779570007552984</v>
       </c>
       <c r="E12" t="n">
         <v>1.2426</v>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.5767195806899652</v>
+        <v>0.576719580689965</v>
       </c>
       <c r="E13" t="n">
         <v>-4.6707</v>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.5766573625528736</v>
+        <v>0.5766573625528737</v>
       </c>
       <c r="E15" t="n">
         <v>6.8796</v>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.5751142091943193</v>
+        <v>0.5751142091943194</v>
       </c>
       <c r="E16" t="n">
         <v>-3.6996</v>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.5741682256922862</v>
+        <v>0.5741682256922861</v>
       </c>
       <c r="E20" t="n">
         <v>0.5593</v>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.5729124802430714</v>
+        <v>0.5729124802430712</v>
       </c>
       <c r="E21" t="n">
         <v>14.4718</v>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6644021289054634</v>
+        <v>0.6644021289054632</v>
       </c>
       <c r="E2" t="n">
         <v>3.6592</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6199052425885558</v>
+        <v>0.6199052425885559</v>
       </c>
       <c r="E6" t="n">
         <v>7.0106</v>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6138062820566276</v>
+        <v>0.6138062820566275</v>
       </c>
       <c r="E10" t="n">
         <v>2.439</v>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.5988567435250562</v>
+        <v>0.5988567435250561</v>
       </c>
       <c r="E16" t="n">
         <v>3.5313</v>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.5943667585538187</v>
+        <v>0.5943667585538186</v>
       </c>
       <c r="E18" t="n">
         <v>5.5125</v>
@@ -6460,7 +6460,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.5924259496958494</v>
+        <v>0.5924259496958493</v>
       </c>
       <c r="E20" t="n">
         <v>-1.8915</v>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.5903178376509044</v>
+        <v>0.5903178376509043</v>
       </c>
       <c r="E21" t="n">
         <v>6.4255</v>

--- a/results/reports/year_2020_report.xlsx
+++ b/results/reports/year_2020_report.xlsx
@@ -655,7 +655,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6416167889110153</v>
+        <v>0.6416167889110155</v>
       </c>
       <c r="E2" t="n">
         <v>4.028</v>
@@ -815,7 +815,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.5992363174497096</v>
+        <v>0.5992363174497097</v>
       </c>
       <c r="E10" t="n">
         <v>3.5108</v>
@@ -895,7 +895,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.5944420282394689</v>
+        <v>0.5944420282394688</v>
       </c>
       <c r="E14" t="n">
         <v>8.261200000000001</v>
@@ -955,7 +955,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5918139786712252</v>
+        <v>0.5918139786712253</v>
       </c>
       <c r="E17" t="n">
         <v>3.3683</v>
@@ -975,7 +975,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.5913450703604394</v>
+        <v>0.5913450703604395</v>
       </c>
       <c r="E18" t="n">
         <v>6.718</v>
@@ -995,7 +995,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.5912339075487211</v>
+        <v>0.5912339075487212</v>
       </c>
       <c r="E19" t="n">
         <v>-1.3614</v>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6355104155971528</v>
+        <v>0.6355104155971529</v>
       </c>
       <c r="E3" t="n">
         <v>-2.2901</v>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.5982303868254891</v>
+        <v>0.598230386825489</v>
       </c>
       <c r="E12" t="n">
         <v>-1.506</v>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.5966664563854562</v>
+        <v>0.5966664563854563</v>
       </c>
       <c r="E13" t="n">
         <v>15.6033</v>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5944468363820878</v>
+        <v>0.5944468363820877</v>
       </c>
       <c r="E17" t="n">
         <v>7.8798</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.593649385301195</v>
+        <v>0.5936493853011949</v>
       </c>
       <c r="E18" t="n">
         <v>0.4423</v>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.5910737839911639</v>
+        <v>0.5910737839911638</v>
       </c>
       <c r="E21" t="n">
         <v>-7.2738</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6415691258513861</v>
+        <v>0.641569125851386</v>
       </c>
       <c r="E2" t="n">
         <v>0.0333</v>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6357095023885563</v>
+        <v>0.6357095023885562</v>
       </c>
       <c r="E3" t="n">
         <v>-0.4823</v>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6164071667253932</v>
+        <v>0.6164071667253931</v>
       </c>
       <c r="E4" t="n">
         <v>-15.0699</v>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6137039986930523</v>
+        <v>0.6137039986930521</v>
       </c>
       <c r="E5" t="n">
         <v>8.349500000000001</v>
@@ -1727,7 +1727,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.5962466714368626</v>
+        <v>0.5962466714368625</v>
       </c>
       <c r="E11" t="n">
         <v>4.7341</v>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.5893941089799585</v>
+        <v>0.5893941089799586</v>
       </c>
       <c r="E16" t="n">
         <v>-3.7037</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.5871722274555846</v>
+        <v>0.5871722274555845</v>
       </c>
       <c r="E20" t="n">
         <v>20.6704</v>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6736048823263801</v>
+        <v>0.6736048823263802</v>
       </c>
       <c r="E3" t="n">
         <v>4.7312</v>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6462394600606328</v>
+        <v>0.6462394600606326</v>
       </c>
       <c r="E4" t="n">
         <v>-0.7667</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.5936289249114506</v>
+        <v>0.5936289249114505</v>
       </c>
       <c r="E16" t="n">
         <v>4.6807</v>
@@ -2293,7 +2293,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5931005495284691</v>
+        <v>0.593100549528469</v>
       </c>
       <c r="E17" t="n">
         <v>22.5942</v>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.5921214430997663</v>
+        <v>0.5921214430997664</v>
       </c>
       <c r="E18" t="n">
         <v>30.4274</v>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.5903937569289361</v>
+        <v>0.5903937569289363</v>
       </c>
       <c r="E20" t="n">
         <v>4.5977</v>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.5899191274517094</v>
+        <v>0.5899191274517095</v>
       </c>
       <c r="E21" t="n">
         <v>10.151</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6777358845041997</v>
+        <v>0.6777358845041996</v>
       </c>
       <c r="E2" t="n">
         <v>-0.258</v>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6527072134771451</v>
+        <v>0.652707213477145</v>
       </c>
       <c r="E3" t="n">
         <v>2.0847</v>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6009097494829645</v>
+        <v>0.6009097494829644</v>
       </c>
       <c r="E8" t="n">
         <v>15.8157</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.5999215621316012</v>
+        <v>0.5999215621316013</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.5971612312277432</v>
+        <v>0.5971612312277433</v>
       </c>
       <c r="E11" t="n">
         <v>19.6586</v>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.5907422658926701</v>
+        <v>0.5907422658926699</v>
       </c>
       <c r="E13" t="n">
         <v>5.1579</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.5890904376722446</v>
+        <v>0.5890904376722444</v>
       </c>
       <c r="E14" t="n">
         <v>-2.0575</v>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.5885041282605641</v>
+        <v>0.588504128260564</v>
       </c>
       <c r="E15" t="n">
         <v>3.4589</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5867019887739784</v>
+        <v>0.5867019887739783</v>
       </c>
       <c r="E17" t="n">
         <v>16.7418</v>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6382427958641638</v>
+        <v>0.6382427958641637</v>
       </c>
       <c r="E2" t="n">
         <v>13.3481</v>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6019391050094134</v>
+        <v>0.6019391050094133</v>
       </c>
       <c r="E6" t="n">
         <v>1.8447</v>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.5974953382398225</v>
+        <v>0.5974953382398224</v>
       </c>
       <c r="E9" t="n">
         <v>15.296</v>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.5917468112951175</v>
+        <v>0.5917468112951176</v>
       </c>
       <c r="E11" t="n">
         <v>-12.4847</v>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.5863855192805971</v>
+        <v>0.586385519280597</v>
       </c>
       <c r="E13" t="n">
         <v>-0.101</v>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.5851456710959645</v>
+        <v>0.5851456710959644</v>
       </c>
       <c r="E14" t="n">
         <v>0.3655</v>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5830697447288588</v>
+        <v>0.5830697447288586</v>
       </c>
       <c r="E17" t="n">
         <v>3.5971</v>
@@ -3225,7 +3225,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.5817359996995191</v>
+        <v>0.5817359996995189</v>
       </c>
       <c r="E19" t="n">
         <v>7</v>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.5800028071029771</v>
+        <v>0.5800028071029772</v>
       </c>
       <c r="E20" t="n">
         <v>-2.8429</v>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.5785307450095839</v>
+        <v>0.5785307450095838</v>
       </c>
       <c r="E21" t="n">
         <v>2.43</v>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.712326316900042</v>
+        <v>0.7123263169000421</v>
       </c>
       <c r="E3" t="n">
         <v>-1.1933</v>
@@ -4010,7 +4010,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6807595109208409</v>
+        <v>0.6807595109208406</v>
       </c>
       <c r="E9" t="n">
         <v>-3.5242</v>
@@ -4110,7 +4110,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6572238529853148</v>
+        <v>0.6572238529853149</v>
       </c>
       <c r="E14" t="n">
         <v>0.5649999999999999</v>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6567303632353009</v>
+        <v>0.656730363235301</v>
       </c>
       <c r="E15" t="n">
         <v>8.2456</v>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6455564595686163</v>
+        <v>0.6455564595686164</v>
       </c>
       <c r="E17" t="n">
         <v>-15.878</v>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.7386294014772729</v>
+        <v>0.738629401477273</v>
       </c>
       <c r="E4" t="n">
         <v>-3.717</v>
@@ -4376,7 +4376,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.7345452931898125</v>
+        <v>0.7345452931898128</v>
       </c>
       <c r="E5" t="n">
         <v>-4.0382</v>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.7142818541820355</v>
+        <v>0.7142818541820354</v>
       </c>
       <c r="E6" t="n">
         <v>2.0539</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6594008978973595</v>
+        <v>0.6594008978973597</v>
       </c>
       <c r="E17" t="n">
         <v>-4.8746</v>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6484091132469745</v>
+        <v>0.6484091132469746</v>
       </c>
       <c r="E20" t="n">
         <v>-5.8824</v>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6480689378742673</v>
+        <v>0.6480689378742671</v>
       </c>
       <c r="E21" t="n">
         <v>-20.6459</v>
@@ -4762,7 +4762,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6402963866833535</v>
+        <v>0.6402963866833536</v>
       </c>
       <c r="E2" t="n">
         <v>-3.0983</v>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.5912148337617085</v>
+        <v>0.5912148337617086</v>
       </c>
       <c r="E5" t="n">
         <v>7.3851</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.5767028683915723</v>
+        <v>0.5767028683915721</v>
       </c>
       <c r="E7" t="n">
         <v>11.3358</v>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.5672275535874168</v>
+        <v>0.5672275535874169</v>
       </c>
       <c r="E9" t="n">
         <v>5.6066</v>
@@ -5228,7 +5228,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6212182931089457</v>
+        <v>0.6212182931089458</v>
       </c>
       <c r="E3" t="n">
         <v>4.2026</v>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.5811118506496938</v>
+        <v>0.5811118506496937</v>
       </c>
       <c r="E13" t="n">
         <v>9.1036</v>
@@ -5468,7 +5468,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.5776568691217169</v>
+        <v>0.577656869121717</v>
       </c>
       <c r="E15" t="n">
         <v>0.1894</v>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.5728289468760606</v>
+        <v>0.5728289468760607</v>
       </c>
       <c r="E19" t="n">
         <v>2.9693</v>
@@ -5674,7 +5674,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6358286834408187</v>
+        <v>0.6358286834408188</v>
       </c>
       <c r="E3" t="n">
         <v>-3.3557</v>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.5922841223474434</v>
+        <v>0.5922841223474433</v>
       </c>
       <c r="E6" t="n">
         <v>0.9827</v>
@@ -5754,7 +5754,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.5903226561585347</v>
+        <v>0.5903226561585349</v>
       </c>
       <c r="E7" t="n">
         <v>-0.0297</v>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.5818075313825884</v>
+        <v>0.5818075313825886</v>
       </c>
       <c r="E9" t="n">
         <v>9.649100000000001</v>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.5787576518032839</v>
+        <v>0.578757651803284</v>
       </c>
       <c r="E10" t="n">
         <v>-2.9534</v>
@@ -5834,7 +5834,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.5786038108505369</v>
+        <v>0.578603810850537</v>
       </c>
       <c r="E11" t="n">
         <v>-1.4765</v>
@@ -5854,7 +5854,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.5779570007552984</v>
+        <v>0.5779570007552983</v>
       </c>
       <c r="E12" t="n">
         <v>1.2426</v>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.576719580689965</v>
+        <v>0.5767195806899651</v>
       </c>
       <c r="E13" t="n">
         <v>-4.6707</v>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.5766641394675376</v>
+        <v>0.5766641394675375</v>
       </c>
       <c r="E14" t="n">
         <v>1.8472</v>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.5729124802430712</v>
+        <v>0.5729124802430714</v>
       </c>
       <c r="E21" t="n">
         <v>14.4718</v>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6644021289054632</v>
+        <v>0.6644021289054634</v>
       </c>
       <c r="E2" t="n">
         <v>3.6592</v>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6138062820566275</v>
+        <v>0.6138062820566276</v>
       </c>
       <c r="E10" t="n">
         <v>2.439</v>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6131099369451861</v>
+        <v>0.6131099369451863</v>
       </c>
       <c r="E11" t="n">
         <v>-2.7778</v>
@@ -6440,7 +6440,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.5932193943133618</v>
+        <v>0.5932193943133617</v>
       </c>
       <c r="E19" t="n">
         <v>-1.8035</v>
@@ -6460,7 +6460,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.5924259496958493</v>
+        <v>0.5924259496958492</v>
       </c>
       <c r="E20" t="n">
         <v>-1.8915</v>
